--- a/data/football/exports/backtesting/football_fixture_backtest_history.xlsx
+++ b/data/football/exports/backtesting/football_fixture_backtest_history.xlsx
@@ -1425,7 +1425,7 @@
       </c>
       <c r="DN2" t="inlineStr">
         <is>
-          <t>2026-05-23 10:20:30</t>
+          <t>2026-05-24 05:37:43</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="DN3" t="inlineStr">
         <is>
-          <t>2026-05-23 10:20:30</t>
+          <t>2026-05-24 05:37:43</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="DN4" t="inlineStr">
         <is>
-          <t>2026-05-23 10:20:30</t>
+          <t>2026-05-24 05:37:43</t>
         </is>
       </c>
     </row>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="DN5" t="inlineStr">
         <is>
-          <t>2026-05-23 10:20:30</t>
+          <t>2026-05-24 05:37:43</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="DN6" t="inlineStr">
         <is>
-          <t>2026-05-23 10:20:30</t>
+          <t>2026-05-24 05:37:43</t>
         </is>
       </c>
     </row>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="DN7" t="inlineStr">
         <is>
-          <t>2026-05-23 10:20:30</t>
+          <t>2026-05-24 05:37:43</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="DN8" t="inlineStr">
         <is>
-          <t>2026-05-23 10:20:30</t>
+          <t>2026-05-24 05:37:43</t>
         </is>
       </c>
     </row>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-23 10:20:30</t>
+          <t>2026-05-24 05:37:43</t>
         </is>
       </c>
     </row>

--- a/data/football/exports/backtesting/football_fixture_backtest_history.xlsx
+++ b/data/football/exports/backtesting/football_fixture_backtest_history.xlsx
@@ -1425,7 +1425,7 @@
       </c>
       <c r="DN2" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:43</t>
+          <t>2026-05-25 14:34:59</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="DN3" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:43</t>
+          <t>2026-05-25 14:34:59</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="DN4" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:43</t>
+          <t>2026-05-25 14:34:59</t>
         </is>
       </c>
     </row>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="DN5" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:43</t>
+          <t>2026-05-25 14:34:59</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="DN6" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:43</t>
+          <t>2026-05-25 14:34:59</t>
         </is>
       </c>
     </row>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="DN7" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:43</t>
+          <t>2026-05-25 14:34:59</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="DN8" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:43</t>
+          <t>2026-05-25 14:34:59</t>
         </is>
       </c>
     </row>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:43</t>
+          <t>2026-05-25 14:34:59</t>
         </is>
       </c>
     </row>

--- a/data/football/exports/backtesting/football_fixture_backtest_history.xlsx
+++ b/data/football/exports/backtesting/football_fixture_backtest_history.xlsx
@@ -1425,7 +1425,7 @@
       </c>
       <c r="DN2" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:59</t>
+          <t>2026-05-26 14:24:14</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="DN3" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:59</t>
+          <t>2026-05-26 14:24:14</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="DN4" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:59</t>
+          <t>2026-05-26 14:24:14</t>
         </is>
       </c>
     </row>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="DN5" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:59</t>
+          <t>2026-05-26 14:24:14</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="DN6" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:59</t>
+          <t>2026-05-26 14:24:14</t>
         </is>
       </c>
     </row>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="DN7" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:59</t>
+          <t>2026-05-26 14:24:14</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="DN8" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:59</t>
+          <t>2026-05-26 14:24:14</t>
         </is>
       </c>
     </row>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:59</t>
+          <t>2026-05-26 14:24:14</t>
         </is>
       </c>
     </row>

--- a/data/football/exports/backtesting/football_fixture_backtest_history.xlsx
+++ b/data/football/exports/backtesting/football_fixture_backtest_history.xlsx
@@ -1425,7 +1425,7 @@
       </c>
       <c r="DN2" t="inlineStr">
         <is>
-          <t>2026-05-26 14:24:14</t>
+          <t>2026-05-27 14:59:08</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="DN3" t="inlineStr">
         <is>
-          <t>2026-05-26 14:24:14</t>
+          <t>2026-05-27 14:59:08</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="DN4" t="inlineStr">
         <is>
-          <t>2026-05-26 14:24:14</t>
+          <t>2026-05-27 14:59:08</t>
         </is>
       </c>
     </row>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="DN5" t="inlineStr">
         <is>
-          <t>2026-05-26 14:24:14</t>
+          <t>2026-05-27 14:59:08</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="DN6" t="inlineStr">
         <is>
-          <t>2026-05-26 14:24:14</t>
+          <t>2026-05-27 14:59:08</t>
         </is>
       </c>
     </row>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="DN7" t="inlineStr">
         <is>
-          <t>2026-05-26 14:24:14</t>
+          <t>2026-05-27 14:59:08</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="DN8" t="inlineStr">
         <is>
-          <t>2026-05-26 14:24:14</t>
+          <t>2026-05-27 14:59:08</t>
         </is>
       </c>
     </row>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-26 14:24:14</t>
+          <t>2026-05-27 14:59:08</t>
         </is>
       </c>
     </row>

--- a/data/football/exports/backtesting/football_fixture_backtest_history.xlsx
+++ b/data/football/exports/backtesting/football_fixture_backtest_history.xlsx
@@ -1425,7 +1425,7 @@
       </c>
       <c r="DN2" t="inlineStr">
         <is>
-          <t>2026-05-27 14:59:08</t>
+          <t>2026-05-28 08:55:11</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="DN3" t="inlineStr">
         <is>
-          <t>2026-05-27 14:59:08</t>
+          <t>2026-05-28 08:55:11</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="DN4" t="inlineStr">
         <is>
-          <t>2026-05-27 14:59:08</t>
+          <t>2026-05-28 08:55:11</t>
         </is>
       </c>
     </row>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="DN5" t="inlineStr">
         <is>
-          <t>2026-05-27 14:59:08</t>
+          <t>2026-05-28 08:55:11</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="DN6" t="inlineStr">
         <is>
-          <t>2026-05-27 14:59:08</t>
+          <t>2026-05-28 08:55:11</t>
         </is>
       </c>
     </row>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="DN7" t="inlineStr">
         <is>
-          <t>2026-05-27 14:59:08</t>
+          <t>2026-05-28 08:55:11</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="DN8" t="inlineStr">
         <is>
-          <t>2026-05-27 14:59:08</t>
+          <t>2026-05-28 08:55:11</t>
         </is>
       </c>
     </row>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-27 14:59:08</t>
+          <t>2026-05-28 08:55:11</t>
         </is>
       </c>
     </row>

--- a/data/football/exports/backtesting/football_fixture_backtest_history.xlsx
+++ b/data/football/exports/backtesting/football_fixture_backtest_history.xlsx
@@ -1425,7 +1425,7 @@
       </c>
       <c r="DN2" t="inlineStr">
         <is>
-          <t>2026-05-28 08:55:11</t>
+          <t>2026-05-28 17:23:18</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="DN3" t="inlineStr">
         <is>
-          <t>2026-05-28 08:55:11</t>
+          <t>2026-05-28 17:23:18</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="DN4" t="inlineStr">
         <is>
-          <t>2026-05-28 08:55:11</t>
+          <t>2026-05-28 17:23:18</t>
         </is>
       </c>
     </row>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="DN5" t="inlineStr">
         <is>
-          <t>2026-05-28 08:55:11</t>
+          <t>2026-05-28 17:23:18</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="DN6" t="inlineStr">
         <is>
-          <t>2026-05-28 08:55:11</t>
+          <t>2026-05-28 17:23:18</t>
         </is>
       </c>
     </row>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="DN7" t="inlineStr">
         <is>
-          <t>2026-05-28 08:55:11</t>
+          <t>2026-05-28 17:23:18</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="DN8" t="inlineStr">
         <is>
-          <t>2026-05-28 08:55:11</t>
+          <t>2026-05-28 17:23:18</t>
         </is>
       </c>
     </row>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-28 08:55:11</t>
+          <t>2026-05-28 17:23:18</t>
         </is>
       </c>
     </row>

--- a/data/football/exports/backtesting/football_fixture_backtest_history.xlsx
+++ b/data/football/exports/backtesting/football_fixture_backtest_history.xlsx
@@ -1425,7 +1425,7 @@
       </c>
       <c r="DN2" t="inlineStr">
         <is>
-          <t>2026-05-28 17:23:18</t>
+          <t>2026-05-28 19:50:39</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="DN3" t="inlineStr">
         <is>
-          <t>2026-05-28 17:23:18</t>
+          <t>2026-05-28 19:50:39</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="DN4" t="inlineStr">
         <is>
-          <t>2026-05-28 17:23:18</t>
+          <t>2026-05-28 19:50:39</t>
         </is>
       </c>
     </row>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="DN5" t="inlineStr">
         <is>
-          <t>2026-05-28 17:23:18</t>
+          <t>2026-05-28 19:50:39</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="DN6" t="inlineStr">
         <is>
-          <t>2026-05-28 17:23:18</t>
+          <t>2026-05-28 19:50:39</t>
         </is>
       </c>
     </row>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="DN7" t="inlineStr">
         <is>
-          <t>2026-05-28 17:23:18</t>
+          <t>2026-05-28 19:50:39</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="DN8" t="inlineStr">
         <is>
-          <t>2026-05-28 17:23:18</t>
+          <t>2026-05-28 19:50:39</t>
         </is>
       </c>
     </row>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-28 17:23:18</t>
+          <t>2026-05-28 19:50:39</t>
         </is>
       </c>
     </row>
